--- a/target/classes/Product Import.xlsx
+++ b/target/classes/Product Import.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BS01361\My Folder\0. Test Type\4. Automation Testing\Selenium Files\MAS_FloraFire\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C10DCB-A164-4B3A-A985-F5416C7720F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EEBD9B-F7B2-4A71-86B9-02677EE70327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -973,35 +973,35 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:X114"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="3"/>
-    <col min="4" max="4" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" style="3"/>
+    <col min="4" max="4" width="15.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="8.85546875" style="1"/>
+    <col min="11" max="11" width="19.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>32</v>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="W2" s="9"/>
       <c r="X2" s="7"/>
     </row>
-    <row r="3" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>37</v>
       </c>
@@ -1207,7 +1207,7 @@
       <c r="W3" s="9"/>
       <c r="X3" s="7"/>
     </row>
-    <row r="4" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="X4" s="7"/>
     </row>
-    <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="X5" s="7"/>
     </row>
-    <row r="6" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>46</v>
       </c>
@@ -1417,7 +1417,7 @@
       <c r="W6" s="10"/>
       <c r="X6" s="7"/>
     </row>
-    <row r="7" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>51</v>
       </c>
@@ -1485,7 +1485,7 @@
       <c r="W7" s="11"/>
       <c r="X7" s="7"/>
     </row>
-    <row r="8" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>54</v>
       </c>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="X8" s="7"/>
     </row>
-    <row r="9" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="X9" s="7"/>
     </row>
-    <row r="10" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>70</v>
       </c>
@@ -1693,498 +1693,498 @@
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
     </row>
-    <row r="11" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
     </row>
-    <row r="18" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
     </row>
-    <row r="20" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="4"/>
       <c r="V20" s="4"/>
       <c r="W20" s="4"/>
     </row>
-    <row r="21" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
     </row>
-    <row r="23" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
     </row>
-    <row r="24" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
     </row>
-    <row r="25" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="4"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
     </row>
-    <row r="26" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
     </row>
-    <row r="27" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
     </row>
-    <row r="28" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
     </row>
-    <row r="29" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
     </row>
-    <row r="30" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
     </row>
-    <row r="31" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D31" s="4"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
     </row>
-    <row r="32" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
     </row>
-    <row r="33" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D33" s="4"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
     </row>
-    <row r="34" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
     </row>
-    <row r="35" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4"/>
     </row>
-    <row r="36" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
     </row>
-    <row r="37" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
     </row>
-    <row r="38" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D38" s="4"/>
       <c r="V38" s="4"/>
       <c r="W38" s="4"/>
     </row>
-    <row r="39" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="4"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
     </row>
-    <row r="40" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
     </row>
-    <row r="41" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="4"/>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
     </row>
-    <row r="42" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
     </row>
-    <row r="43" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
     </row>
-    <row r="44" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
     </row>
-    <row r="45" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
     </row>
-    <row r="46" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
     </row>
-    <row r="47" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
     </row>
-    <row r="48" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D48" s="4"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
     </row>
-    <row r="49" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D49" s="4"/>
       <c r="V49" s="4"/>
       <c r="W49" s="4"/>
     </row>
-    <row r="50" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D50" s="4"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
     </row>
-    <row r="51" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D51" s="4"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
     </row>
-    <row r="52" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
     </row>
-    <row r="53" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D53" s="4"/>
       <c r="V53" s="4"/>
       <c r="W53" s="4"/>
     </row>
-    <row r="54" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D54" s="4"/>
       <c r="V54" s="4"/>
       <c r="W54" s="4"/>
     </row>
-    <row r="55" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D55" s="4"/>
       <c r="V55" s="4"/>
       <c r="W55" s="4"/>
     </row>
-    <row r="56" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D56" s="4"/>
       <c r="V56" s="4"/>
       <c r="W56" s="4"/>
     </row>
-    <row r="57" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D57" s="4"/>
       <c r="V57" s="4"/>
       <c r="W57" s="4"/>
     </row>
-    <row r="58" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D58" s="4"/>
       <c r="V58" s="4"/>
       <c r="W58" s="4"/>
     </row>
-    <row r="59" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D59" s="4"/>
       <c r="V59" s="4"/>
       <c r="W59" s="4"/>
     </row>
-    <row r="60" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D60" s="4"/>
       <c r="V60" s="4"/>
       <c r="W60" s="4"/>
     </row>
-    <row r="61" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D61" s="4"/>
       <c r="V61" s="4"/>
       <c r="W61" s="4"/>
     </row>
-    <row r="62" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D62" s="4"/>
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
     </row>
-    <row r="63" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D63" s="4"/>
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
     </row>
-    <row r="64" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D64" s="4"/>
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
     </row>
-    <row r="65" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D65" s="4"/>
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
     </row>
-    <row r="66" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D66" s="4"/>
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
     </row>
-    <row r="67" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D67" s="4"/>
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
     </row>
-    <row r="68" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D68" s="4"/>
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
     </row>
-    <row r="69" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D69" s="4"/>
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
     </row>
-    <row r="70" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D70" s="4"/>
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
     </row>
-    <row r="71" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D71" s="4"/>
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
     </row>
-    <row r="72" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D72" s="4"/>
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
     </row>
-    <row r="73" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D73" s="4"/>
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
     </row>
-    <row r="74" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D74" s="4"/>
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
     </row>
-    <row r="75" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D75" s="4"/>
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
     </row>
-    <row r="76" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D76" s="4"/>
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
     </row>
-    <row r="77" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D77" s="4"/>
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
     </row>
-    <row r="78" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D78" s="4"/>
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
     </row>
-    <row r="79" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D79" s="4"/>
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
     </row>
-    <row r="80" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D80" s="4"/>
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
     </row>
-    <row r="81" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="4"/>
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
     </row>
-    <row r="82" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D82" s="4"/>
       <c r="V82" s="4"/>
       <c r="W82" s="4"/>
     </row>
-    <row r="83" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D83" s="4"/>
       <c r="V83" s="4"/>
       <c r="W83" s="4"/>
     </row>
-    <row r="84" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D84" s="4"/>
       <c r="V84" s="4"/>
       <c r="W84" s="4"/>
     </row>
-    <row r="85" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D85" s="4"/>
       <c r="V85" s="4"/>
       <c r="W85" s="4"/>
     </row>
-    <row r="86" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D86" s="4"/>
       <c r="V86" s="4"/>
       <c r="W86" s="4"/>
     </row>
-    <row r="87" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D87" s="4"/>
       <c r="V87" s="4"/>
       <c r="W87" s="4"/>
     </row>
-    <row r="88" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D88" s="4"/>
       <c r="V88" s="4"/>
       <c r="W88" s="4"/>
     </row>
-    <row r="89" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D89" s="4"/>
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
     </row>
-    <row r="90" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D90" s="4"/>
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
     </row>
-    <row r="91" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D91" s="4"/>
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
     </row>
-    <row r="92" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D92" s="4"/>
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
     </row>
-    <row r="93" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D93" s="4"/>
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
     </row>
-    <row r="94" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D94" s="4"/>
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
     </row>
-    <row r="95" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D95" s="4"/>
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
     </row>
-    <row r="96" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D96" s="4"/>
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
     </row>
-    <row r="97" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D97" s="4"/>
       <c r="V97" s="4"/>
       <c r="W97" s="4"/>
     </row>
-    <row r="98" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D98" s="4"/>
       <c r="V98" s="4"/>
       <c r="W98" s="4"/>
     </row>
-    <row r="99" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D99" s="4"/>
       <c r="V99" s="4"/>
       <c r="W99" s="4"/>
     </row>
-    <row r="100" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D100" s="4"/>
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
     </row>
-    <row r="101" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D101" s="4"/>
       <c r="V101" s="4"/>
       <c r="W101" s="4"/>
     </row>
-    <row r="102" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D102" s="4"/>
       <c r="V102" s="4"/>
       <c r="W102" s="4"/>
     </row>
-    <row r="103" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D103" s="4"/>
       <c r="V103" s="4"/>
       <c r="W103" s="4"/>
     </row>
-    <row r="104" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D104" s="4"/>
       <c r="V104" s="4"/>
       <c r="W104" s="4"/>
     </row>
-    <row r="105" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D105" s="4"/>
       <c r="V105" s="4"/>
       <c r="W105" s="4"/>
     </row>
-    <row r="106" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D106" s="4"/>
       <c r="V106" s="4"/>
       <c r="W106" s="4"/>
     </row>
-    <row r="107" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D107" s="4"/>
       <c r="V107" s="4"/>
       <c r="W107" s="4"/>
     </row>
-    <row r="108" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D108" s="4"/>
       <c r="V108" s="4"/>
       <c r="W108" s="4"/>
     </row>
-    <row r="109" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D109" s="4"/>
       <c r="V109" s="4"/>
       <c r="W109" s="4"/>
     </row>
-    <row r="110" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D110" s="4"/>
       <c r="V110" s="4"/>
       <c r="W110" s="4"/>
     </row>
-    <row r="111" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D111" s="4"/>
       <c r="V111" s="4"/>
       <c r="W111" s="4"/>
     </row>
-    <row r="112" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D112" s="4"/>
       <c r="V112" s="4"/>
       <c r="W112" s="4"/>
     </row>
-    <row r="113" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D113" s="4"/>
       <c r="V113" s="4"/>
       <c r="W113" s="4"/>
     </row>
-    <row r="114" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D114" s="4"/>
       <c r="V114" s="4"/>
       <c r="W114" s="4"/>
